--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_06-05-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_06-05-2025.xlsx
@@ -134,6 +134,166 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £11.39</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £13.25</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £13.35</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £16.90</t>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £16.21</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £18.07</t>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £18.45</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £22.99</t>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £22.21</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.60</t>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.30</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.48</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £28.88</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £26.82</t>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £29.90</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.83</t>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.83</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.83</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.75</t>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.95</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £37.44</t>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £36.86</t>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £41.59</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £46.80</t>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £45.51</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.12</t>
+      </text>
+    </comment>
+    <comment ref="D16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.12</t>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.12</t>
+      </text>
+    </comment>
+    <comment ref="H16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.10</t>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £45.85</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1822,5 +1982,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>